--- a/deliverables/PBCP-BH-04_rev4.xlsx
+++ b/deliverables/PBCP-BH-04_rev4.xlsx
@@ -12732,8 +12732,10 @@
       <c r="D14" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>40</v>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GWL analisis likuefaksi (Report BP-00-GEO-RPT-003)</t>
+        </is>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -12765,13 +12767,15 @@
         <v>45</v>
       </c>
       <c r="C16" s="8">
-        <v>18.5</v>
+        <v>19.6</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="7" t="s">
-        <v>47</v>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Report Tabel 5.1</t>
+        </is>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -12782,13 +12786,15 @@
         <v>49</v>
       </c>
       <c r="C17" s="8">
-        <v>18.399999999999999</v>
+        <v>20.2</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E17" s="7" t="s">
-        <v>47</v>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Report Tabel 5.1</t>
+        </is>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -12943,8 +12949,10 @@
       <c r="D26" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E26" s="7" t="s">
-        <v>70</v>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sesuai perhitungan sebelumnya</t>
+        </is>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -12958,8 +12966,10 @@
       <c r="D27" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E27" s="7" t="s">
-        <v>70</v>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sesuai perhitungan sebelumnya</t>
+        </is>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -13199,7 +13209,11 @@
       <c r="D45" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E45" s="7"/>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DD_max tidak difaktorkan (beban faktor 1,0)</t>
+        </is>
+      </c>
     </row>
     <row r="47" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
@@ -13218,12 +13232,16 @@
         <v>9</v>
       </c>
       <c r="C48" s="14">
-        <v>3000</v>
+        <v>5152.9</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E48" s="7"/>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GROUP WPD 2 cellar 4x1, ASD2(max) - beban lama, update dgn GROUP beban revisi</t>
+        </is>
+      </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
@@ -13233,12 +13251,16 @@
         <v>13</v>
       </c>
       <c r="C49" s="14">
-        <v>600</v>
+        <v>1583.9</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E49" s="7"/>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GROUP WPD 2 cellar 4x1, LRFD3 - beban lama, update dgn GROUP beban revisi</t>
+        </is>
+      </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
@@ -13248,12 +13270,16 @@
         <v>18</v>
       </c>
       <c r="C50" s="14">
-        <v>500</v>
+        <v>1101.5</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E50" s="7"/>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GROUP WPD 2 cellar 4x1, ASD1 (DL) - beban lama, update dgn GROUP beban revisi</t>
+        </is>
+      </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
@@ -13263,12 +13289,16 @@
         <v>108</v>
       </c>
       <c r="C51" s="14">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E51" s="7"/>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GROUP: tidak ada tiang tarik pada kombinasi yang ditinjau</t>
+        </is>
+      </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
@@ -13468,8 +13498,10 @@
       <c r="G7" s="11">
         <v>0</v>
       </c>
-      <c r="H7" s="6" t="s">
-        <v>128</v>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I7" s="16">
         <f>IF(F7="Clay",Input!$C$32*G7,0)</f>
@@ -13517,8 +13549,10 @@
       <c r="G8" s="11">
         <v>5</v>
       </c>
-      <c r="H8" s="6" t="s">
-        <v>128</v>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I8" s="20">
         <f>IF(F8="Clay",Input!$C$32*G8,0)</f>
@@ -13568,8 +13602,10 @@
       <c r="G9" s="11">
         <v>49</v>
       </c>
-      <c r="H9" s="6" t="s">
-        <v>128</v>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I9" s="16">
         <f>IF(F9="Clay",Input!$C$32*G9,0)</f>
@@ -13619,8 +13655,10 @@
       <c r="G10" s="11">
         <v>44</v>
       </c>
-      <c r="H10" s="6" t="s">
-        <v>128</v>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I10" s="20">
         <f>IF(F10="Clay",Input!$C$32*G10,0)</f>
@@ -13668,8 +13706,10 @@
       <c r="G11" s="11">
         <v>30</v>
       </c>
-      <c r="H11" s="6" t="s">
-        <v>128</v>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I11" s="16">
         <f>IF(F11="Clay",Input!$C$32*G11,0)</f>
@@ -13719,8 +13759,10 @@
       <c r="G12" s="11">
         <v>14</v>
       </c>
-      <c r="H12" s="22" t="s">
-        <v>128</v>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I12" s="20">
         <f>IF(F12="Clay",Input!$C$32*G12,0)</f>
@@ -13770,8 +13812,10 @@
       <c r="G13" s="11">
         <v>12</v>
       </c>
-      <c r="H13" s="22" t="s">
-        <v>128</v>
+      <c r="H13" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I13" s="16">
         <f>IF(F13="Clay",Input!$C$32*G13,0)</f>
@@ -13821,8 +13865,10 @@
       <c r="G14" s="11">
         <v>18</v>
       </c>
-      <c r="H14" s="22" t="s">
-        <v>129</v>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L</t>
+        </is>
       </c>
       <c r="I14" s="20">
         <f>IF(F14="Clay",Input!$C$32*G14,0)</f>
@@ -13872,8 +13918,10 @@
       <c r="G15" s="11">
         <v>26</v>
       </c>
-      <c r="H15" s="22" t="s">
-        <v>129</v>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L</t>
+        </is>
       </c>
       <c r="I15" s="16">
         <f>IF(F15="Clay",Input!$C$32*G15,0)</f>
@@ -13923,8 +13971,10 @@
       <c r="G16" s="11">
         <v>15</v>
       </c>
-      <c r="H16" s="22" t="s">
-        <v>128</v>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I16" s="20">
         <f>IF(F16="Clay",Input!$C$32*G16,0)</f>
@@ -13974,8 +14024,10 @@
       <c r="G17" s="11">
         <v>15</v>
       </c>
-      <c r="H17" s="22" t="s">
-        <v>128</v>
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I17" s="16">
         <f>IF(F17="Clay",Input!$C$32*G17,0)</f>
@@ -14025,8 +14077,10 @@
       <c r="G18" s="11">
         <v>21</v>
       </c>
-      <c r="H18" s="22" t="s">
-        <v>128</v>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I18" s="20">
         <f>IF(F18="Clay",Input!$C$32*G18,0)</f>
@@ -14076,8 +14130,10 @@
       <c r="G19" s="11">
         <v>18</v>
       </c>
-      <c r="H19" s="22" t="s">
-        <v>128</v>
+      <c r="H19" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L</t>
+        </is>
       </c>
       <c r="I19" s="16">
         <f>IF(F19="Clay",Input!$C$32*G19,0)</f>
@@ -14127,8 +14183,10 @@
       <c r="G20" s="11">
         <v>41</v>
       </c>
-      <c r="H20" s="22" t="s">
-        <v>128</v>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I20" s="20">
         <f>IF(F20="Clay",Input!$C$32*G20,0)</f>
@@ -14178,8 +14236,10 @@
       <c r="G21" s="11">
         <v>36</v>
       </c>
-      <c r="H21" s="6" t="s">
-        <v>128</v>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I21" s="16">
         <f>IF(F21="Clay",Input!$C$32*G21,0)</f>
@@ -14229,8 +14289,10 @@
       <c r="G22" s="11">
         <v>35</v>
       </c>
-      <c r="H22" s="6" t="s">
-        <v>128</v>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I22" s="20">
         <f>IF(F22="Clay",Input!$C$32*G22,0)</f>
@@ -14278,8 +14340,10 @@
       <c r="G23" s="11">
         <v>24</v>
       </c>
-      <c r="H23" s="6" t="s">
-        <v>128</v>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I23" s="16">
         <f>IF(F23="Clay",Input!$C$32*G23,0)</f>
@@ -14327,8 +14391,10 @@
       <c r="G24" s="11">
         <v>21</v>
       </c>
-      <c r="H24" s="6" t="s">
-        <v>128</v>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I24" s="20">
         <f>IF(F24="Clay",Input!$C$32*G24,0)</f>
@@ -14348,7 +14414,11 @@
       <c r="N24" s="20">
         <f>IF(F24="Clay",Input!$C$35*I24,MIN(Input!$C$33*G24,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O24" s="21"/>
+      <c r="O24" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-01 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P24" s="11"/>
       <c r="Q24" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B24),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14376,8 +14446,10 @@
       <c r="G25" s="11">
         <v>21</v>
       </c>
-      <c r="H25" s="6" t="s">
-        <v>128</v>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I25" s="16">
         <f>IF(F25="Clay",Input!$C$32*G25,0)</f>
@@ -14397,7 +14469,11 @@
       <c r="N25" s="16">
         <f>IF(F25="Clay",Input!$C$35*I25,MIN(Input!$C$33*G25,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O25" s="17"/>
+      <c r="O25" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-01 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P25" s="11"/>
       <c r="Q25" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B25),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14425,8 +14501,10 @@
       <c r="G26" s="11">
         <v>48</v>
       </c>
-      <c r="H26" s="6" t="s">
-        <v>128</v>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I26" s="20">
         <f>IF(F26="Clay",Input!$C$32*G26,0)</f>
@@ -14446,7 +14524,11 @@
       <c r="N26" s="20">
         <f>IF(F26="Clay",Input!$C$35*I26,MIN(Input!$C$33*G26,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O26" s="21"/>
+      <c r="O26" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-01 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P26" s="11"/>
       <c r="Q26" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B26),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14474,8 +14556,10 @@
       <c r="G27" s="11">
         <v>50</v>
       </c>
-      <c r="H27" s="6" t="s">
-        <v>128</v>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I27" s="16">
         <f>IF(F27="Clay",Input!$C$32*G27,0)</f>
@@ -14495,7 +14579,11 @@
       <c r="N27" s="16">
         <f>IF(F27="Clay",Input!$C$35*I27,MIN(Input!$C$33*G27,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O27" s="17"/>
+      <c r="O27" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-01 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P27" s="11"/>
       <c r="Q27" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B27),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14523,8 +14611,10 @@
       <c r="G28" s="11">
         <v>50</v>
       </c>
-      <c r="H28" s="6" t="s">
-        <v>128</v>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I28" s="20">
         <f>IF(F28="Clay",Input!$C$32*G28,0)</f>
@@ -14544,7 +14634,11 @@
       <c r="N28" s="20">
         <f>IF(F28="Clay",Input!$C$35*I28,MIN(Input!$C$33*G28,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O28" s="21"/>
+      <c r="O28" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-01 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P28" s="11"/>
       <c r="Q28" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B28),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14572,8 +14666,10 @@
       <c r="G29" s="11">
         <v>50</v>
       </c>
-      <c r="H29" s="6" t="s">
-        <v>128</v>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I29" s="16">
         <f>IF(F29="Clay",Input!$C$32*G29,0)</f>
@@ -14593,7 +14689,11 @@
       <c r="N29" s="16">
         <f>IF(F29="Clay",Input!$C$35*I29,MIN(Input!$C$33*G29,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O29" s="17"/>
+      <c r="O29" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-01 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P29" s="11"/>
       <c r="Q29" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B29),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14621,8 +14721,10 @@
       <c r="G30" s="11">
         <v>50</v>
       </c>
-      <c r="H30" s="6" t="s">
-        <v>128</v>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I30" s="20">
         <f>IF(F30="Clay",Input!$C$32*G30,0)</f>
@@ -14642,7 +14744,11 @@
       <c r="N30" s="20">
         <f>IF(F30="Clay",Input!$C$35*I30,MIN(Input!$C$33*G30,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O30" s="21"/>
+      <c r="O30" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-01 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P30" s="11"/>
       <c r="Q30" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B30),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14670,8 +14776,10 @@
       <c r="G31" s="11">
         <v>50</v>
       </c>
-      <c r="H31" s="6" t="s">
-        <v>128</v>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I31" s="16">
         <f>IF(F31="Clay",Input!$C$32*G31,0)</f>
@@ -14691,7 +14799,11 @@
       <c r="N31" s="16">
         <f>IF(F31="Clay",Input!$C$35*I31,MIN(Input!$C$33*G31,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O31" s="17"/>
+      <c r="O31" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-01 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P31" s="11"/>
       <c r="Q31" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B31),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14719,8 +14831,10 @@
       <c r="G32" s="11">
         <v>50</v>
       </c>
-      <c r="H32" s="6" t="s">
-        <v>128</v>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I32" s="20">
         <f>IF(F32="Clay",Input!$C$32*G32,0)</f>
@@ -14740,7 +14854,11 @@
       <c r="N32" s="20">
         <f>IF(F32="Clay",Input!$C$35*I32,MIN(Input!$C$33*G32,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O32" s="21"/>
+      <c r="O32" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-01 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P32" s="11"/>
       <c r="Q32" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B32),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14768,8 +14886,10 @@
       <c r="G33" s="11">
         <v>50</v>
       </c>
-      <c r="H33" s="6" t="s">
-        <v>128</v>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I33" s="16">
         <f>IF(F33="Clay",Input!$C$32*G33,0)</f>
@@ -14789,7 +14909,11 @@
       <c r="N33" s="16">
         <f>IF(F33="Clay",Input!$C$35*I33,MIN(Input!$C$33*G33,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O33" s="17"/>
+      <c r="O33" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-01 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P33" s="11"/>
       <c r="Q33" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B33),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14817,8 +14941,10 @@
       <c r="G34" s="11">
         <v>50</v>
       </c>
-      <c r="H34" s="6" t="s">
-        <v>128</v>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I34" s="20">
         <f>IF(F34="Clay",Input!$C$32*G34,0)</f>
@@ -14838,7 +14964,11 @@
       <c r="N34" s="20">
         <f>IF(F34="Clay",Input!$C$35*I34,MIN(Input!$C$33*G34,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O34" s="21"/>
+      <c r="O34" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-01 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P34" s="11"/>
       <c r="Q34" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B34),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14866,8 +14996,10 @@
       <c r="G35" s="11">
         <v>50</v>
       </c>
-      <c r="H35" s="6" t="s">
-        <v>128</v>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I35" s="16">
         <f>IF(F35="Clay",Input!$C$32*G35,0)</f>
@@ -14887,7 +15019,11 @@
       <c r="N35" s="16">
         <f>IF(F35="Clay",Input!$C$35*I35,MIN(Input!$C$33*G35,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O35" s="17"/>
+      <c r="O35" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-01 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P35" s="11"/>
       <c r="Q35" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B35),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14915,8 +15051,10 @@
       <c r="G36" s="11">
         <v>50</v>
       </c>
-      <c r="H36" s="6" t="s">
-        <v>128</v>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I36" s="20">
         <f>IF(F36="Clay",Input!$C$32*G36,0)</f>
@@ -14936,7 +15074,11 @@
       <c r="N36" s="20">
         <f>IF(F36="Clay",Input!$C$35*I36,MIN(Input!$C$33*G36,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O36" s="21"/>
+      <c r="O36" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-01 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P36" s="11"/>
       <c r="Q36" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B36),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14964,8 +15106,10 @@
       <c r="G37" s="11">
         <v>33</v>
       </c>
-      <c r="H37" s="6" t="s">
-        <v>128</v>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I37" s="16">
         <f>IF(F37="Clay",Input!$C$32*G37,0)</f>
@@ -14985,7 +15129,11 @@
       <c r="N37" s="16">
         <f>IF(F37="Clay",Input!$C$35*I37,MIN(Input!$C$33*G37,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O37" s="17"/>
+      <c r="O37" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-01 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P37" s="11"/>
       <c r="Q37" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B37),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -15013,8 +15161,10 @@
       <c r="G38" s="11">
         <v>36</v>
       </c>
-      <c r="H38" s="6" t="s">
-        <v>128</v>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I38" s="20">
         <f>IF(F38="Clay",Input!$C$32*G38,0)</f>
@@ -15034,7 +15184,11 @@
       <c r="N38" s="20">
         <f>IF(F38="Clay",Input!$C$35*I38,MIN(Input!$C$33*G38,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O38" s="21"/>
+      <c r="O38" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-01 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P38" s="11"/>
       <c r="Q38" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B38),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -15062,8 +15216,10 @@
       <c r="G39" s="11">
         <v>31</v>
       </c>
-      <c r="H39" s="6" t="s">
-        <v>128</v>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I39" s="16">
         <f>IF(F39="Clay",Input!$C$32*G39,0)</f>
@@ -15083,7 +15239,11 @@
       <c r="N39" s="16">
         <f>IF(F39="Clay",Input!$C$35*I39,MIN(Input!$C$33*G39,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O39" s="17"/>
+      <c r="O39" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-01 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P39" s="11"/>
       <c r="Q39" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B39),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -15111,8 +15271,10 @@
       <c r="G40" s="11">
         <v>30</v>
       </c>
-      <c r="H40" s="6" t="s">
-        <v>128</v>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I40" s="20">
         <f>IF(F40="Clay",Input!$C$32*G40,0)</f>
@@ -15132,7 +15294,11 @@
       <c r="N40" s="20">
         <f>IF(F40="Clay",Input!$C$35*I40,MIN(Input!$C$33*G40,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O40" s="21"/>
+      <c r="O40" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-01 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P40" s="11"/>
       <c r="Q40" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B40),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -15160,8 +15326,10 @@
       <c r="G41" s="11">
         <v>34</v>
       </c>
-      <c r="H41" s="6" t="s">
-        <v>128</v>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I41" s="16">
         <f>IF(F41="Clay",Input!$C$32*G41,0)</f>
@@ -15181,7 +15349,11 @@
       <c r="N41" s="16">
         <f>IF(F41="Clay",Input!$C$35*I41,MIN(Input!$C$33*G41,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O41" s="17"/>
+      <c r="O41" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-01 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P41" s="11"/>
       <c r="Q41" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B41),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -15209,8 +15381,10 @@
       <c r="G42" s="11">
         <v>31</v>
       </c>
-      <c r="H42" s="6" t="s">
-        <v>128</v>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I42" s="20">
         <f>IF(F42="Clay",Input!$C$32*G42,0)</f>
@@ -15230,7 +15404,11 @@
       <c r="N42" s="20">
         <f>IF(F42="Clay",Input!$C$35*I42,MIN(Input!$C$33*G42,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O42" s="21"/>
+      <c r="O42" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-01 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P42" s="11"/>
       <c r="Q42" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B42),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -15258,8 +15436,10 @@
       <c r="G43" s="11">
         <v>29</v>
       </c>
-      <c r="H43" s="6" t="s">
-        <v>128</v>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I43" s="16">
         <f>IF(F43="Clay",Input!$C$32*G43,0)</f>
@@ -15279,7 +15459,11 @@
       <c r="N43" s="16">
         <f>IF(F43="Clay",Input!$C$35*I43,MIN(Input!$C$33*G43,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O43" s="17"/>
+      <c r="O43" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-01 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P43" s="11"/>
       <c r="Q43" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B43),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -15307,8 +15491,10 @@
       <c r="G44" s="11">
         <v>25</v>
       </c>
-      <c r="H44" s="6" t="s">
-        <v>128</v>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I44" s="20">
         <f>IF(F44="Clay",Input!$C$32*G44,0)</f>
@@ -15328,7 +15514,11 @@
       <c r="N44" s="20">
         <f>IF(F44="Clay",Input!$C$35*I44,MIN(Input!$C$33*G44,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O44" s="21"/>
+      <c r="O44" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-01 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P44" s="11"/>
       <c r="Q44" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B44),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -15356,8 +15546,10 @@
       <c r="G45" s="11">
         <v>35</v>
       </c>
-      <c r="H45" s="6" t="s">
-        <v>128</v>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I45" s="16">
         <f>IF(F45="Clay",Input!$C$32*G45,0)</f>
@@ -15377,7 +15569,11 @@
       <c r="N45" s="16">
         <f>IF(F45="Clay",Input!$C$35*I45,MIN(Input!$C$33*G45,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O45" s="17"/>
+      <c r="O45" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-01 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P45" s="11"/>
       <c r="Q45" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B45),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -15405,8 +15601,10 @@
       <c r="G46" s="11">
         <v>42</v>
       </c>
-      <c r="H46" s="6" t="s">
-        <v>128</v>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I46" s="20">
         <f>IF(F46="Clay",Input!$C$32*G46,0)</f>
@@ -15426,7 +15624,11 @@
       <c r="N46" s="20">
         <f>IF(F46="Clay",Input!$C$35*I46,MIN(Input!$C$33*G46,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O46" s="21"/>
+      <c r="O46" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-01 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P46" s="11"/>
       <c r="Q46" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B46),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -15454,8 +15656,10 @@
       <c r="G47" s="11">
         <v>46</v>
       </c>
-      <c r="H47" s="6" t="s">
-        <v>128</v>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I47" s="16">
         <f>IF(F47="Clay",Input!$C$32*G47,0)</f>
@@ -15475,7 +15679,11 @@
       <c r="N47" s="16">
         <f>IF(F47="Clay",Input!$C$35*I47,MIN(Input!$C$33*G47,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O47" s="17"/>
+      <c r="O47" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-01 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P47" s="11"/>
       <c r="Q47" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B47),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>

--- a/deliverables/PBCP-BH-04_rev4.xlsx
+++ b/deliverables/PBCP-BH-04_rev4.xlsx
@@ -13232,14 +13232,14 @@
         <v>9</v>
       </c>
       <c r="C48" s="14">
-        <v>5152.9</v>
+        <v>3000.0</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">GROUP WPD 2 cellar 4x1, ASD2(max) - beban lama, update dgn GROUP beban revisi</t>
+          <t xml:space="preserve">beban seragam semua BH (sama dengan BH-03) - update dgn GROUP beban revisi</t>
         </is>
       </c>
     </row>
@@ -13251,14 +13251,14 @@
         <v>13</v>
       </c>
       <c r="C49" s="14">
-        <v>1583.9</v>
+        <v>600.0</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">GROUP WPD 2 cellar 4x1, LRFD3 - beban lama, update dgn GROUP beban revisi</t>
+          <t xml:space="preserve">beban seragam semua BH (sama dengan BH-03) - update dgn GROUP beban revisi</t>
         </is>
       </c>
     </row>
@@ -13270,14 +13270,14 @@
         <v>18</v>
       </c>
       <c r="C50" s="14">
-        <v>1101.5</v>
+        <v>500.0</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">GROUP WPD 2 cellar 4x1, ASD1 (DL) - beban lama, update dgn GROUP beban revisi</t>
+          <t xml:space="preserve">beban seragam semua BH (sama dengan BH-03) - update dgn GROUP beban revisi</t>
         </is>
       </c>
     </row>
@@ -13296,7 +13296,7 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">GROUP: tidak ada tiang tarik pada kombinasi yang ditinjau</t>
+          <t xml:space="preserve">tidak ada tiang tarik pada kombinasi yang ditinjau</t>
         </is>
       </c>
     </row>
